--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Animali domestici.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Animali domestici.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="100">
   <si>
     <r>
       <t xml:space="preserve">
@@ -828,7 +828,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -898,22 +898,8 @@
     </r>
   </si>
   <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mancato pagamento
 Il seguente messaggio serve a sollecitare il cittadino per il mancato pagamento ma non costituisce in alcun modo un avviso a valore legale (i.e. notifica).</t>
-  </si>
-  <si>
-    <t>L'invio di questo messaggio serve a comunicare al cittadino i passi successivi alla chiusura della pratica. Se la chiusura della pratica non implica alcuna azione successiva, consigliamo di non inviare questo messaggio.</t>
   </si>
 </sst>
 </file>
@@ -1717,22 +1703,22 @@
         <v>98</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>56</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
